--- a/ValueSet-mii-vs-mikrobio-organismen-snomedct.xlsx
+++ b/ValueSet-mii-vs-mikrobio-organismen-snomedct.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-mii-vs-mikrobio-organismen-snomedct.xlsx
+++ b/ValueSet-mii-vs-mikrobio-organismen-snomedct.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot2</t>
   </si>
   <si>
     <t>Name</t>
